--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-careplan.xlsx
@@ -380,7 +380,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>CarePlan.meta.versionId</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-careplan.xlsx
@@ -440,7 +440,7 @@
     <t>CarePlan.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -536,7 +536,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -652,7 +652,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|ActivityDefinition|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -690,7 +690,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -743,7 +743,7 @@
     <t>CarePlan.status</t>
   </si>
   <si>
-    <t>下書き| アクティブ| 保留中| 取り消された| 完了| エラーで入力| 不明</t>
+    <t>下書き| アクティブ| 保留中| 取り消された| 完了 | エラー入力| 不明</t>
   </si>
   <si>
     <t>計画が実行中か、将来の意図を表しているか、現在歴史的記録であるかを示します。</t>
@@ -823,7 +823,7 @@
     <t>「これが複数存在する計画の区別を支援するための「種類」の計画である」（たとえば、「在宅医療」、「精神医療」、「喘息」、「疾患管理」など）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-category</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -860,7 +860,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -885,14 +885,14 @@
     <t>CarePlan.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
-    <t>一部として作成されたEncounter（診察、受診、入退院など）</t>
-  </si>
-  <si>
-    <t>このCarePlanが作成されたEncounter（診察、受診、入退院など）、またはこの記録の作成に密接に関係するEncounter（診察、受診、入退院など）。</t>
+    <t>一部として作成された受療行動</t>
+  </si>
+  <si>
+    <t>このCarePlanが作成された受療行動、またはこの記録の作成に密接に関係する受療行動。</t>
   </si>
   <si>
     <t>これは通常、イベントが発生したエンカウンター内で行われますが、公式的なエンカウンターの完了前または後でも、エンカウンターの文脈に関連するアクティビティが開始される場合があります。 ケアプランに従って実施されるケアプランアクティビティは、他のエンカウンターの一部として行われる可能性があります。</t>
@@ -974,7 +974,7 @@
     <t>CarePlan.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|RelatedPerson|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1008,7 +1008,7 @@
     <t>CarePlan.careTeam</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1030,7 +1030,7 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition)
+    <t xml:space="preserve">Reference(Condition|4.0.1)
 </t>
   </si>
   <si>
@@ -1061,7 +1061,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal)
+    <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
   </si>
   <si>
@@ -1170,13 +1170,13 @@
     <t>活動の結果を特定します。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
   </si>
   <si>
-    <t>予約、Encounter（診察、受診、入退院など）、手続きなど。</t>
+    <t>予約、受療行動、手続きなど。</t>
   </si>
   <si>
     <t>アクティビティによって生じる結果や行動の詳細。プロシジャー（処置等）、エンカウンター、観察などの「イベント」リソースに参照していることは、アクティビティそのものの結果/成果です。CarePlan.activity.detailを使用するか、CarePlan.activity.reference（「リクエスト」リソースへの参照）を使用してアクティビティを伝えることができます。</t>
@@ -1222,7 +1222,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|MedicationRequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup)
+    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
 </t>
   </si>
   <si>
@@ -1293,7 +1293,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1315,7 +1315,7 @@
     <t>活動の詳細タイプ</t>
   </si>
   <si>
-    <t>計画された活動の詳細な説明；例えば、どのようなラボテスト、どのようなプロシジャー（処置等）、どのようなEncounter（診察、受診、入退院など）か。</t>
+    <t>計画された活動の詳細な説明；例えば、どのようなラボテスト、どのようなプロシジャー（処置等）、どのような受療行動か。</t>
   </si>
   <si>
     <t>特定の製品に関する活動においては、あまり関係がない傾向があります。コードに否定を示すことは避け、代わりに「禁止」としてください。</t>
@@ -1324,10 +1324,10 @@
     <t>Allows matching performed to planned as well as validation against protocols.</t>
   </si>
   <si>
-    <t>活動の種類に関する詳細な説明例：どのような実験、どのプロシジャー（処置等）、どのようなEncounter（診察、受診、入退院など）ですか。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>活動の種類に関する詳細な説明例：どのような実験、どのプロシジャー（処置等）、どのような受療行動ですか。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1354,7 +1354,7 @@
     <t>看護計画のアクティビティが必要な理由を特定する。一般的な健康状態コード、予防、手術の準備などの概念を含めることができる。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1363,7 +1363,7 @@
     <t>CarePlan.activity.detail.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1484,7 +1484,7 @@
     <t>CarePlan.activity.detail.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1509,7 +1509,7 @@
     <t>CarePlan.activity.detail.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|RelatedPerson|Patient|CareTeam|HealthcareService|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|RelatedPerson|4.0.1|Patient|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1535,7 +1535,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|Substance)</t>
+Reference(Medication|4.0.1|Substance|4.0.1)</t>
   </si>
   <si>
     <t>何を管理/供給するのですか？</t>
@@ -1547,7 +1547,7 @@
     <t>ケア・プランのアクティビティーの一環として提供される製品またはアレンジメント</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -1563,7 +1563,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1941,17 +1941,17 @@
   <dimension ref="A1:AN69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.58203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.58203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="143.37890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="163.6796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1960,26 +1960,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="76.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.859375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="65.9765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.24609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="55.8046875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="173.13671875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="145.83984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="47.84375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="148.43359375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="125.03125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2782,7 +2782,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -9878,12 +9878,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN69">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-careplan.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
